--- a/health_coach_forms/024_health_and_fitness_training_form--health_coach_forms.xlsx
+++ b/health_coach_forms/024_health_and_fitness_training_form--health_coach_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1131,12 +1131,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'primary_caregiver',_'label':_'primary_caregiver'}</t>
+          <t>primary_caregiver</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Primary Caregiver', 'label': 'Primary Caregiver'}</t>
+          <t>Primary Caregiver</t>
         </is>
       </c>
     </row>
@@ -1148,12 +1148,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'emergency_contact',_'label':_'emergency_contact'}</t>
+          <t>emergency_contact</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Emergency Contact', 'label': 'Emergency Contact'}</t>
+          <t>Emergency Contact</t>
         </is>
       </c>
     </row>
@@ -1165,12 +1165,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'daily',_'label':_'daily'}</t>
+          <t>daily</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Daily', 'label': 'Daily'}</t>
+          <t>Daily</t>
         </is>
       </c>
     </row>
@@ -1182,12 +1182,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'weekly',_'label':_'weekly'}</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Weekly', 'label': 'Weekly'}</t>
+          <t>Weekly</t>
         </is>
       </c>
     </row>
@@ -1199,12 +1199,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'monthly',_'label':_'monthly'}</t>
+          <t>monthly</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'Monthly', 'label': 'Monthly'}</t>
+          <t>Monthly</t>
         </is>
       </c>
     </row>
@@ -1216,12 +1216,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'beginner',_'label':_'beginner'}</t>
+          <t>beginner</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Beginner', 'label': 'Beginner'}</t>
+          <t>Beginner</t>
         </is>
       </c>
     </row>
@@ -1233,12 +1233,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'intermediate',_'label':_'intermediate'}</t>
+          <t>intermediate</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Intermediate', 'label': 'Intermediate'}</t>
+          <t>Intermediate</t>
         </is>
       </c>
     </row>
@@ -1250,12 +1250,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'advanced',_'label':_'advanced'}</t>
+          <t>advanced</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'Advanced', 'label': 'Advanced'}</t>
+          <t>Advanced</t>
         </is>
       </c>
     </row>
@@ -1267,12 +1267,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'morning',_'label':_'morning'}</t>
+          <t>morning</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Morning', 'label': 'Morning'}</t>
+          <t>Morning</t>
         </is>
       </c>
     </row>
@@ -1284,12 +1284,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'afternoon',_'label':_'afternoon'}</t>
+          <t>afternoon</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Afternoon', 'label': 'Afternoon'}</t>
+          <t>Afternoon</t>
         </is>
       </c>
     </row>
@@ -1301,12 +1301,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'evening',_'label':_'evening'}</t>
+          <t>evening</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'Evening', 'label': 'Evening'}</t>
+          <t>Evening</t>
         </is>
       </c>
     </row>
@@ -1318,12 +1318,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'monday',_'label':_'monday'}</t>
+          <t>monday</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Monday', 'label': 'Monday'}</t>
+          <t>Monday</t>
         </is>
       </c>
     </row>
@@ -1335,12 +1335,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'tuesday',_'label':_'tuesday'}</t>
+          <t>tuesday</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Tuesday', 'label': 'Tuesday'}</t>
+          <t>Tuesday</t>
         </is>
       </c>
     </row>
@@ -1352,12 +1352,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'wednesday',_'label':_'wednesday'}</t>
+          <t>wednesday</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'Wednesday', 'label': 'Wednesday'}</t>
+          <t>Wednesday</t>
         </is>
       </c>
     </row>
@@ -1369,12 +1369,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'id':_4,_'name':_'thursday',_'label':_'thursday'}</t>
+          <t>thursday</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'id': 4, 'name': 'Thursday', 'label': 'Thursday'}</t>
+          <t>Thursday</t>
         </is>
       </c>
     </row>
@@ -1386,12 +1386,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'id':_5,_'name':_'friday',_'label':_'friday'}</t>
+          <t>friday</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'id': 5, 'name': 'Friday', 'label': 'Friday'}</t>
+          <t>Friday</t>
         </is>
       </c>
     </row>
@@ -1403,12 +1403,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'id':_6,_'name':_'saturday',_'label':_'saturday'}</t>
+          <t>saturday</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'id': 6, 'name': 'Saturday', 'label': 'Saturday'}</t>
+          <t>Saturday</t>
         </is>
       </c>
     </row>
@@ -1420,12 +1420,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'id':_7,_'name':_'sunday',_'label':_'sunday'}</t>
+          <t>sunday</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'id': 7, 'name': 'Sunday', 'label': 'Sunday'}</t>
+          <t>Sunday</t>
         </is>
       </c>
     </row>
@@ -1437,12 +1437,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'weight_loss',_'label':_'weight_loss'}</t>
+          <t>weight_loss</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Weight Loss', 'label': 'Weight Loss'}</t>
+          <t>Weight Loss</t>
         </is>
       </c>
     </row>
@@ -1454,12 +1454,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'strength_training',_'label':_'strength_training'}</t>
+          <t>strength_training</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Strength Training', 'label': 'Strength Training'}</t>
+          <t>Strength Training</t>
         </is>
       </c>
     </row>
@@ -1471,12 +1471,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'cardio',_'label':_'cardio'}</t>
+          <t>cardio</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'Cardio', 'label': 'Cardio'}</t>
+          <t>Cardio</t>
         </is>
       </c>
     </row>
@@ -1488,12 +1488,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>{'id':_4,_'name':_'endurance',_'label':_'endurance'}</t>
+          <t>endurance</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>{'id': 4, 'name': 'Endurance', 'label': 'Endurance'}</t>
+          <t>Endurance</t>
         </is>
       </c>
     </row>
@@ -1505,12 +1505,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>{'id':_5,_'name':_'balance',_'label':_'balance'}</t>
+          <t>balance</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>{'id': 5, 'name': 'Balance', 'label': 'Balance'}</t>
+          <t>Balance</t>
         </is>
       </c>
     </row>
@@ -1522,12 +1522,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>{'id':_6,_'name':_'flexibility',_'label':_'flexibility'}</t>
+          <t>flexibility</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>{'id': 6, 'name': 'Flexibility', 'label': 'Flexibility'}</t>
+          <t>Flexibility</t>
         </is>
       </c>
     </row>
@@ -1539,12 +1539,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>{'id':_7,_'name':_'mobility',_'label':_'mobility'}</t>
+          <t>mobility</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>{'id': 7, 'name': 'Mobility', 'label': 'Mobility'}</t>
+          <t>Mobility</t>
         </is>
       </c>
     </row>
@@ -1556,12 +1556,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>{'id':_8,_'name':_'power',_'label':_'power'}</t>
+          <t>power</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>{'id': 8, 'name': 'Power', 'label': 'Power'}</t>
+          <t>Power</t>
         </is>
       </c>
     </row>
@@ -1573,12 +1573,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>{'id':_9,_'name':_'strength_training_with_a_focus_on_core_strengthening',_'label':_'strength_training_with_a_focus_on_core_strengthening'}</t>
+          <t>strength_training_with_a_focus_on_core_strengthening</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>{'id': 9, 'name': 'Strength Training with a focus on Core Strengthening', 'label': 'Strength Training with a focus on Core Strengthening'}</t>
+          <t>Strength Training with a focus on Core Strengthening</t>
         </is>
       </c>
     </row>
@@ -1590,12 +1590,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>{'id':_10,_'name':_'strength_training_with_a_focus_on_endurance',_'label':_'strength_training_with_a_focus_on_endurance'}</t>
+          <t>strength_training_with_a_focus_on_endurance</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>{'id': 10, 'name': 'Strength Training with a focus on Endurance', 'label': 'Strength Training with a focus on Endurance'}</t>
+          <t>Strength Training with a focus on Endurance</t>
         </is>
       </c>
     </row>
@@ -1607,12 +1607,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>{'id':_11,_'name':_'yoga',_'label':_'yoga'}</t>
+          <t>yoga</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>{'id': 11, 'name': 'Yoga', 'label': 'Yoga'}</t>
+          <t>Yoga</t>
         </is>
       </c>
     </row>
@@ -1624,12 +1624,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>{'id':_12,_'name':_'pilates',_'label':_'pilates'}</t>
+          <t>pilates</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>{'id': 12, 'name': 'Pilates', 'label': 'Pilates'}</t>
+          <t>Pilates</t>
         </is>
       </c>
     </row>
@@ -1641,12 +1641,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>{'id':_13,_'name':_'high-intensity_interval_training_(hiit)',_'label':_'high-intensity_interval_training_(hiit)'}</t>
+          <t>high-intensity_interval_training_(hiit)</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>{'id': 13, 'name': 'High-Intensity Interval Training (HIIT)', 'label': 'High-Intensity Interval Training (HIIT)'}</t>
+          <t>High-Intensity Interval Training (HIIT)</t>
         </is>
       </c>
     </row>
@@ -1658,12 +1658,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>{'id':_14,_'name':_'low-intensity_long-duration_cardio',_'label':_'low-intensity_long-duration_cardio'}</t>
+          <t>low-intensity_long-duration_cardio</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>{'id': 14, 'name': 'Low-Intensity Long-Duration Cardio', 'label': 'Low-Intensity Long-Duration Cardio'}</t>
+          <t>Low-Intensity Long-Duration Cardio</t>
         </is>
       </c>
     </row>
@@ -1675,12 +1675,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>{'id':_15,_'name':_'flexibility_and_mobility',_'label':_'flexibility_and_mobility'}</t>
+          <t>flexibility_and_mobility</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>{'id': 15, 'name': 'Flexibility and Mobility', 'label': 'Flexibility and Mobility'}</t>
+          <t>Flexibility and Mobility</t>
         </is>
       </c>
     </row>
@@ -1692,12 +1692,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>{'id':_16,_'name':_'balance_and_flexibility',_'label':_'balance_and_flexibility'}</t>
+          <t>balance_and_flexibility</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>{'id': 16, 'name': 'Balance and Flexibility', 'label': 'Balance and Flexibility'}</t>
+          <t>Balance and Flexibility</t>
         </is>
       </c>
     </row>
@@ -1709,12 +1709,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'daily',_'label':_'daily'}</t>
+          <t>daily</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Daily', 'label': 'Daily'}</t>
+          <t>Daily</t>
         </is>
       </c>
     </row>
@@ -1726,12 +1726,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'weekly',_'label':_'weekly'}</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Weekly', 'label': 'Weekly'}</t>
+          <t>Weekly</t>
         </is>
       </c>
     </row>
@@ -1743,12 +1743,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'monthly',_'label':_'monthly'}</t>
+          <t>monthly</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'Monthly', 'label': 'Monthly'}</t>
+          <t>Monthly</t>
         </is>
       </c>
     </row>
@@ -1760,12 +1760,12 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'weekly',_'label':_'weekly'}</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Weekly', 'label': 'Weekly'}</t>
+          <t>Weekly</t>
         </is>
       </c>
     </row>
@@ -1777,12 +1777,12 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'bi-weekly',_'label':_'bi-weekly'}</t>
+          <t>bi-weekly</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Bi-Weekly', 'label': 'Bi-Weekly'}</t>
+          <t>Bi-Weekly</t>
         </is>
       </c>
     </row>
@@ -1794,12 +1794,12 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'monthly',_'label':_'monthly'}</t>
+          <t>monthly</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'Monthly', 'label': 'Monthly'}</t>
+          <t>Monthly</t>
         </is>
       </c>
     </row>
@@ -1811,12 +1811,12 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'active',_'label':_'active'}</t>
+          <t>active</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Active', 'label': 'Active'}</t>
+          <t>Active</t>
         </is>
       </c>
     </row>
@@ -1828,12 +1828,12 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'inactive',_'label':_'inactive'}</t>
+          <t>inactive</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Inactive', 'label': 'Inactive'}</t>
+          <t>Inactive</t>
         </is>
       </c>
     </row>
